--- a/stories/arbres/TREE-REL-016.xlsx
+++ b/stories/arbres/TREE-REL-016.xlsx
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -831,6 +831,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -845,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV87"/>
+  <dimension ref="A1:AW87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1139,6 +1151,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1301,6 +1318,11 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Lila est dans le train avec maman. À la gare, elles vont au parc. Un camarade bouscule. Lila dit stop. Lila s'éloigne. Elle rejoint maman. Maman est le parent au parc. Papa arrive au banc.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1487,6 +1509,11 @@
         <v>8</v>
       </c>
       <c r="AV3" s="2" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1649,6 +1676,11 @@
         <v>8</v>
       </c>
       <c r="AV4" s="2" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|C'est le matin. Une feuille tombe. Au parc, un camarade bouscule. Lila dit stop. Lila s'éloigne. Elle va vers maman, le parent au parc.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1825,6 +1857,11 @@
       <c r="AV5" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Un camarade bouscule Lila. Que fait-elle ?</t>
         </is>
       </c>
     </row>
@@ -1993,6 +2030,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. Stop. Lila s'éloigne. Maman est le parent au parc. On continue.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2179,6 +2221,11 @@
         <v>8</v>
       </c>
       <c r="AV7" s="2" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2341,6 +2388,11 @@
         <v>8</v>
       </c>
       <c r="AV8" s="2" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>narrateur|Lila pose le ballon rouge. On entend un oiseau. Encore trop près. Lila dit stop. Lila s'éloigne. Maman, le parent au parc, est au banc. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2529,6 +2581,11 @@
       <c r="AV9" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -2693,6 +2750,11 @@
         <v>8</v>
       </c>
       <c r="AV10" s="2" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>narrateur|Tom s'approche trop près. Une feuille tombe. Lila dit stop. Lila s'éloigne. Le ballon rouge reste près du banc. Lila rejoint maman, le parent au parc. Merci maman.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2855,6 +2917,11 @@
         <v>8</v>
       </c>
       <c r="AV11" s="2" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3017,6 +3084,11 @@
         <v>8</v>
       </c>
       <c r="AV12" s="2" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>narrateur|Léa s'approche trop près. Le vent est doux. Lila dit stop. Lila s'éloigne. Le ballon rouge reste près du banc. Lila rejoint maman, le parent au parc. Merci maman.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3179,6 +3251,11 @@
         <v>8</v>
       </c>
       <c r="AV13" s="2" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3341,6 +3418,11 @@
         <v>8</v>
       </c>
       <c r="AV14" s="2" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>narrateur|Sami s'approche trop près. On entend un oiseau. Lila dit stop. Lila s'éloigne. Le ballon rouge reste près du banc. Lila rejoint maman, le parent au parc. Merci maman.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3503,6 +3585,11 @@
         <v>8</v>
       </c>
       <c r="AV15" s="2" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3665,6 +3752,11 @@
         <v>8</v>
       </c>
       <c r="AV16" s="2" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>narrateur|Lila pose le seau bleu. Ça sent l'herbe coupée. Encore trop près. Lila dit stop. Lila s'éloigne. Maman, le parent au parc, est au banc. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3853,6 +3945,11 @@
       <c r="AV17" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -4017,6 +4114,11 @@
         <v>8</v>
       </c>
       <c r="AV18" s="2" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>narrateur|Tom s'approche trop près. Le vent est doux. Lila dit stop. Lila s'éloigne. Le seau bleu reste près du banc. Lila rejoint maman, le parent au parc. Merci maman.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4179,6 +4281,11 @@
         <v>8</v>
       </c>
       <c r="AV19" s="2" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4341,6 +4448,11 @@
         <v>8</v>
       </c>
       <c r="AV20" s="2" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>narrateur|Léa s'approche trop près. On entend un oiseau. Lila dit stop. Lila s'éloigne. Le seau bleu reste près du banc. Lila rejoint maman, le parent au parc. Merci maman.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4503,6 +4615,11 @@
         <v>8</v>
       </c>
       <c r="AV21" s="2" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4665,6 +4782,11 @@
         <v>8</v>
       </c>
       <c r="AV22" s="2" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>narrateur|Sami s'approche trop près. Ça sent l'herbe coupée. Lila dit stop. Lila s'éloigne. Le seau bleu reste près du banc. Lila rejoint maman, le parent au parc. Merci maman.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4827,6 +4949,11 @@
         <v>8</v>
       </c>
       <c r="AV23" s="2" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -4989,6 +5116,11 @@
         <v>8</v>
       </c>
       <c r="AV24" s="2" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>narrateur|Lila pose le doudou. Le soleil chauffe un peu. Encore trop près. Lila dit stop. Lila s'éloigne. Maman, le parent au parc, est au banc. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5177,6 +5309,11 @@
       <c r="AV25" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -5341,6 +5478,11 @@
         <v>8</v>
       </c>
       <c r="AV26" s="2" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>narrateur|Tom s'approche trop près. On entend un oiseau. Lila dit stop. Lila s'éloigne. Le doudou reste près du banc. Lila rejoint maman, le parent au parc. Merci maman.</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5503,6 +5645,11 @@
         <v>8</v>
       </c>
       <c r="AV27" s="2" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5665,6 +5812,11 @@
         <v>8</v>
       </c>
       <c r="AV28" s="2" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>narrateur|Léa s'approche trop près. Ça sent l'herbe coupée. Lila dit stop. Lila s'éloigne. Le doudou reste près du banc. Lila rejoint maman, le parent au parc. Merci maman.</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5827,6 +5979,11 @@
         <v>8</v>
       </c>
       <c r="AV29" s="2" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -5989,6 +6146,11 @@
         <v>8</v>
       </c>
       <c r="AV30" s="2" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>narrateur|Sami s'approche trop près. Le soleil chauffe un peu. Lila dit stop. Lila s'éloigne. Le doudou reste près du banc. Lila rejoint maman, le parent au parc. Merci maman.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6151,6 +6313,11 @@
         <v>8</v>
       </c>
       <c r="AV31" s="2" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6313,6 +6480,11 @@
         <v>8</v>
       </c>
       <c r="AV32" s="2" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>narrateur|C'est après la sieste. Le vent est doux. Au parc, un camarade bouscule. Lila dit stop. Lila s'éloigne. Elle va vers maman, le parent au parc.</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6489,6 +6661,11 @@
       <c r="AV33" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>narrateur|Un camarade bouscule Lila. Que fait-elle ?</t>
         </is>
       </c>
     </row>
@@ -6657,6 +6834,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. Stop. Lila s'éloigne. Maman est le parent au parc. On continue.</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -6843,6 +7025,11 @@
         <v>8</v>
       </c>
       <c r="AV35" s="2" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -7005,6 +7192,11 @@
         <v>8</v>
       </c>
       <c r="AV36" s="2" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>narrateur|Lila pose le ballon rouge. On entend un oiseau. Encore trop près. Lila dit stop. Lila s'éloigne. Maman, le parent au parc, est au banc. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7193,6 +7385,11 @@
       <c r="AV37" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -7357,6 +7554,11 @@
         <v>8</v>
       </c>
       <c r="AV38" s="2" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>narrateur|Tom s'approche trop près. Le vent est doux. Lila dit stop. Lila s'éloigne. Le ballon rouge reste près du banc. Lila rejoint maman, le parent au parc. Merci maman.</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7519,6 +7721,11 @@
         <v>8</v>
       </c>
       <c r="AV39" s="2" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7681,6 +7888,11 @@
         <v>8</v>
       </c>
       <c r="AV40" s="2" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>narrateur|Léa s'approche trop près. On entend un oiseau. Lila dit stop. Lila s'éloigne. Le ballon rouge reste près du banc. Lila rejoint maman, le parent au parc. Merci maman.</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -7843,6 +8055,11 @@
         <v>8</v>
       </c>
       <c r="AV41" s="2" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -8005,6 +8222,11 @@
         <v>8</v>
       </c>
       <c r="AV42" s="2" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>narrateur|Sami s'approche trop près. Ça sent l'herbe coupée. Lila dit stop. Lila s'éloigne. Le ballon rouge reste près du banc. Lila rejoint maman, le parent au parc. Merci maman.</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8167,6 +8389,11 @@
         <v>8</v>
       </c>
       <c r="AV43" s="2" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8329,6 +8556,11 @@
         <v>8</v>
       </c>
       <c r="AV44" s="2" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>narrateur|Lila pose le seau bleu. Ça sent l'herbe coupée. Encore trop près. Lila dit stop. Lila s'éloigne. Maman, le parent au parc, est au banc. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8517,6 +8749,11 @@
       <c r="AV45" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -8681,6 +8918,11 @@
         <v>8</v>
       </c>
       <c r="AV46" s="2" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>narrateur|Tom s'approche trop près. On entend un oiseau. Lila dit stop. Lila s'éloigne. Le seau bleu reste près du banc. Lila rejoint maman, le parent au parc. Merci maman.</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -8843,6 +9085,11 @@
         <v>8</v>
       </c>
       <c r="AV47" s="2" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -9005,6 +9252,11 @@
         <v>8</v>
       </c>
       <c r="AV48" s="2" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>narrateur|Léa s'approche trop près. Ça sent l'herbe coupée. Lila dit stop. Lila s'éloigne. Le seau bleu reste près du banc. Lila rejoint maman, le parent au parc. Merci maman.</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9167,6 +9419,11 @@
         <v>8</v>
       </c>
       <c r="AV49" s="2" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9329,6 +9586,11 @@
         <v>8</v>
       </c>
       <c r="AV50" s="2" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>narrateur|Sami s'approche trop près. Le soleil chauffe un peu. Lila dit stop. Lila s'éloigne. Le seau bleu reste près du banc. Lila rejoint maman, le parent au parc. Merci maman.</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9491,6 +9753,11 @@
         <v>8</v>
       </c>
       <c r="AV51" s="2" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9653,6 +9920,11 @@
         <v>8</v>
       </c>
       <c r="AV52" s="2" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>narrateur|Lila pose le doudou. Le soleil chauffe un peu. Encore trop près. Lila dit stop. Lila s'éloigne. Maman, le parent au parc, est au banc. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -9841,6 +10113,11 @@
       <c r="AV53" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -10005,6 +10282,11 @@
         <v>8</v>
       </c>
       <c r="AV54" s="2" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>narrateur|Tom s'approche trop près. Ça sent l'herbe coupée. Lila dit stop. Lila s'éloigne. Le doudou reste près du banc. Lila rejoint maman, le parent au parc. Merci maman.</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10167,6 +10449,11 @@
         <v>8</v>
       </c>
       <c r="AV55" s="2" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10329,6 +10616,11 @@
         <v>8</v>
       </c>
       <c r="AV56" s="2" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>narrateur|Léa s'approche trop près. Le soleil chauffe un peu. Lila dit stop. Lila s'éloigne. Le doudou reste près du banc. Lila rejoint maman, le parent au parc. Merci maman.</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10491,6 +10783,11 @@
         <v>8</v>
       </c>
       <c r="AV57" s="2" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10653,6 +10950,11 @@
         <v>8</v>
       </c>
       <c r="AV58" s="2" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>narrateur|Sami s'approche trop près. Le sol est frais. Lila dit stop. Lila s'éloigne. Le doudou reste près du banc. Lila rejoint maman, le parent au parc. Merci maman.</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -10815,6 +11117,11 @@
         <v>8</v>
       </c>
       <c r="AV59" s="2" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -10977,6 +11284,11 @@
         <v>8</v>
       </c>
       <c r="AV60" s="2" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>narrateur|C'est le soir. On entend un oiseau. Au parc, un camarade bouscule. Lila dit stop. Lila s'éloigne. Elle va vers maman, le parent au parc.</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11153,6 +11465,11 @@
       <c r="AV61" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>narrateur|Un camarade bouscule Lila. Que fait-elle ?</t>
         </is>
       </c>
     </row>
@@ -11321,6 +11638,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. Stop. Lila s'éloigne. Maman est le parent au parc. On continue.</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11507,6 +11829,11 @@
         <v>8</v>
       </c>
       <c r="AV63" s="2" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -11669,6 +11996,11 @@
         <v>8</v>
       </c>
       <c r="AV64" s="2" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>narrateur|Lila pose le ballon rouge. On entend un oiseau. Encore trop près. Lila dit stop. Lila s'éloigne. Maman, le parent au parc, est au banc. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -11857,6 +12189,11 @@
       <c r="AV65" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -12021,6 +12358,11 @@
         <v>8</v>
       </c>
       <c r="AV66" s="2" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>narrateur|Tom s'approche trop près. On entend un oiseau. Lila dit stop. Lila s'éloigne. Le ballon rouge reste près du banc. Lila rejoint maman, le parent au parc. Merci maman.</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12183,6 +12525,11 @@
         <v>8</v>
       </c>
       <c r="AV67" s="2" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12345,6 +12692,11 @@
         <v>8</v>
       </c>
       <c r="AV68" s="2" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>narrateur|Léa s'approche trop près. Ça sent l'herbe coupée. Lila dit stop. Lila s'éloigne. Le ballon rouge reste près du banc. Lila rejoint maman, le parent au parc. Merci maman.</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12507,6 +12859,11 @@
         <v>8</v>
       </c>
       <c r="AV69" s="2" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -12669,6 +13026,11 @@
         <v>8</v>
       </c>
       <c r="AV70" s="2" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>narrateur|Sami s'approche trop près. Le soleil chauffe un peu. Lila dit stop. Lila s'éloigne. Le ballon rouge reste près du banc. Lila rejoint maman, le parent au parc. Merci maman.</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -12831,6 +13193,11 @@
         <v>8</v>
       </c>
       <c r="AV71" s="2" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -12993,6 +13360,11 @@
         <v>8</v>
       </c>
       <c r="AV72" s="2" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>narrateur|Lila pose le seau bleu. Ça sent l'herbe coupée. Encore trop près. Lila dit stop. Lila s'éloigne. Maman, le parent au parc, est au banc. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13181,6 +13553,11 @@
       <c r="AV73" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -13345,6 +13722,11 @@
         <v>8</v>
       </c>
       <c r="AV74" s="2" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>narrateur|Tom s'approche trop près. Ça sent l'herbe coupée. Lila dit stop. Lila s'éloigne. Le seau bleu reste près du banc. Lila rejoint maman, le parent au parc. Merci maman.</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13507,6 +13889,11 @@
         <v>8</v>
       </c>
       <c r="AV75" s="2" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -13669,6 +14056,11 @@
         <v>8</v>
       </c>
       <c r="AV76" s="2" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>narrateur|Léa s'approche trop près. Le soleil chauffe un peu. Lila dit stop. Lila s'éloigne. Le seau bleu reste près du banc. Lila rejoint maman, le parent au parc. Merci maman.</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -13831,6 +14223,11 @@
         <v>8</v>
       </c>
       <c r="AV77" s="2" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -13993,6 +14390,11 @@
         <v>8</v>
       </c>
       <c r="AV78" s="2" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>narrateur|Sami s'approche trop près. Le sol est frais. Lila dit stop. Lila s'éloigne. Le seau bleu reste près du banc. Lila rejoint maman, le parent au parc. Merci maman.</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14155,6 +14557,11 @@
         <v>8</v>
       </c>
       <c r="AV79" s="2" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14317,6 +14724,11 @@
         <v>8</v>
       </c>
       <c r="AV80" s="2" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>narrateur|Lila pose le doudou. Le soleil chauffe un peu. Encore trop près. Lila dit stop. Lila s'éloigne. Maman, le parent au parc, est au banc. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14505,6 +14917,11 @@
       <c r="AV81" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -14669,6 +15086,11 @@
         <v>8</v>
       </c>
       <c r="AV82" s="2" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>narrateur|Tom s'approche trop près. Le soleil chauffe un peu. Lila dit stop. Lila s'éloigne. Le doudou reste près du banc. Lila rejoint maman, le parent au parc. Merci maman.</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -14831,6 +15253,11 @@
         <v>8</v>
       </c>
       <c r="AV83" s="2" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -14993,6 +15420,11 @@
         <v>8</v>
       </c>
       <c r="AV84" s="2" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>narrateur|Léa s'approche trop près. Le sol est frais. Lila dit stop. Lila s'éloigne. Le doudou reste près du banc. Lila rejoint maman, le parent au parc. Merci maman.</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15155,6 +15587,11 @@
         <v>8</v>
       </c>
       <c r="AV85" s="2" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15317,6 +15754,11 @@
         <v>8</v>
       </c>
       <c r="AV86" s="2" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>narrateur|Sami s'approche trop près. Un petit bruit d'eau. Lila dit stop. Lila s'éloigne. Le doudou reste près du banc. Lila rejoint maman, le parent au parc. Merci maman.</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15479,6 +15921,11 @@
         <v>8</v>
       </c>
       <c r="AV87" s="2" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15497,7 +15944,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A10"/>
+  <dimension ref="A1:A11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -15570,6 +16017,13 @@
       <c r="A10" t="inlineStr">
         <is>
           <t>ch3C3: prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/TREE-REL-016.xlsx
+++ b/stories/arbres/TREE-REL-016.xlsx
@@ -857,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW87"/>
+  <dimension ref="A1:AX87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1156,6 +1156,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1323,6 +1328,11 @@
           <t>narrateur|Lila est dans le train avec maman. À la gare, elles vont au parc. Un camarade bouscule. Lila dit stop. Lila s'éloigne. Elle rejoint maman. Maman est le parent au parc. Papa arrive au banc.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1514,6 +1524,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1681,6 +1692,11 @@
           <t>narrateur|C'est le matin. Une feuille tombe. Au parc, un camarade bouscule. Lila dit stop. Lila s'éloigne. Elle va vers maman, le parent au parc.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1864,6 +1880,7 @@
           <t>narrateur|Un camarade bouscule Lila. Que fait-elle ?</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2035,6 +2052,11 @@
           <t>narrateur|Oui. Stop. Lila s'éloigne. Maman est le parent au parc. On continue.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2226,6 +2248,7 @@
           <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
         </is>
       </c>
+      <c r="AX7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2393,6 +2416,11 @@
           <t>narrateur|Lila pose le ballon rouge. On entend un oiseau. Encore trop près. Lila dit stop. Lila s'éloigne. Maman, le parent au parc, est au banc. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2588,6 +2616,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2755,6 +2784,11 @@
           <t>narrateur|Tom s'approche trop près. Une feuille tombe. Lila dit stop. Lila s'éloigne. Le ballon rouge reste près du banc. Lila rejoint maman, le parent au parc. Merci maman.</t>
         </is>
       </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2922,6 +2956,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3089,6 +3124,11 @@
           <t>narrateur|Léa s'approche trop près. Le vent est doux. Lila dit stop. Lila s'éloigne. Le ballon rouge reste près du banc. Lila rejoint maman, le parent au parc. Merci maman.</t>
         </is>
       </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3256,6 +3296,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3423,6 +3464,11 @@
           <t>narrateur|Sami s'approche trop près. On entend un oiseau. Lila dit stop. Lila s'éloigne. Le ballon rouge reste près du banc. Lila rejoint maman, le parent au parc. Merci maman.</t>
         </is>
       </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3590,6 +3636,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3757,6 +3804,11 @@
           <t>narrateur|Lila pose le seau bleu. Ça sent l'herbe coupée. Encore trop près. Lila dit stop. Lila s'éloigne. Maman, le parent au parc, est au banc. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3952,6 +4004,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -4119,6 +4172,11 @@
           <t>narrateur|Tom s'approche trop près. Le vent est doux. Lila dit stop. Lila s'éloigne. Le seau bleu reste près du banc. Lila rejoint maman, le parent au parc. Merci maman.</t>
         </is>
       </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4286,6 +4344,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4453,6 +4512,11 @@
           <t>narrateur|Léa s'approche trop près. On entend un oiseau. Lila dit stop. Lila s'éloigne. Le seau bleu reste près du banc. Lila rejoint maman, le parent au parc. Merci maman.</t>
         </is>
       </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4620,6 +4684,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4787,6 +4852,11 @@
           <t>narrateur|Sami s'approche trop près. Ça sent l'herbe coupée. Lila dit stop. Lila s'éloigne. Le seau bleu reste près du banc. Lila rejoint maman, le parent au parc. Merci maman.</t>
         </is>
       </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4954,6 +5024,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -5121,6 +5192,11 @@
           <t>narrateur|Lila pose le doudou. Le soleil chauffe un peu. Encore trop près. Lila dit stop. Lila s'éloigne. Maman, le parent au parc, est au banc. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5316,6 +5392,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5483,6 +5560,11 @@
           <t>narrateur|Tom s'approche trop près. On entend un oiseau. Lila dit stop. Lila s'éloigne. Le doudou reste près du banc. Lila rejoint maman, le parent au parc. Merci maman.</t>
         </is>
       </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5650,6 +5732,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5817,6 +5900,11 @@
           <t>narrateur|Léa s'approche trop près. Ça sent l'herbe coupée. Lila dit stop. Lila s'éloigne. Le doudou reste près du banc. Lila rejoint maman, le parent au parc. Merci maman.</t>
         </is>
       </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5984,6 +6072,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -6151,6 +6240,11 @@
           <t>narrateur|Sami s'approche trop près. Le soleil chauffe un peu. Lila dit stop. Lila s'éloigne. Le doudou reste près du banc. Lila rejoint maman, le parent au parc. Merci maman.</t>
         </is>
       </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6318,6 +6412,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6485,6 +6580,11 @@
           <t>narrateur|C'est après la sieste. Le vent est doux. Au parc, un camarade bouscule. Lila dit stop. Lila s'éloigne. Elle va vers maman, le parent au parc.</t>
         </is>
       </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6668,6 +6768,7 @@
           <t>narrateur|Un camarade bouscule Lila. Que fait-elle ?</t>
         </is>
       </c>
+      <c r="AX33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -6839,6 +6940,11 @@
           <t>narrateur|Oui. Stop. Lila s'éloigne. Maman est le parent au parc. On continue.</t>
         </is>
       </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -7030,6 +7136,7 @@
           <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
         </is>
       </c>
+      <c r="AX35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -7197,6 +7304,11 @@
           <t>narrateur|Lila pose le ballon rouge. On entend un oiseau. Encore trop près. Lila dit stop. Lila s'éloigne. Maman, le parent au parc, est au banc. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7392,6 +7504,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7559,6 +7672,11 @@
           <t>narrateur|Tom s'approche trop près. Le vent est doux. Lila dit stop. Lila s'éloigne. Le ballon rouge reste près du banc. Lila rejoint maman, le parent au parc. Merci maman.</t>
         </is>
       </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7726,6 +7844,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7893,6 +8012,11 @@
           <t>narrateur|Léa s'approche trop près. On entend un oiseau. Lila dit stop. Lila s'éloigne. Le ballon rouge reste près du banc. Lila rejoint maman, le parent au parc. Merci maman.</t>
         </is>
       </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -8060,6 +8184,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -8227,6 +8352,11 @@
           <t>narrateur|Sami s'approche trop près. Ça sent l'herbe coupée. Lila dit stop. Lila s'éloigne. Le ballon rouge reste près du banc. Lila rejoint maman, le parent au parc. Merci maman.</t>
         </is>
       </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8394,6 +8524,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8561,6 +8692,11 @@
           <t>narrateur|Lila pose le seau bleu. Ça sent l'herbe coupée. Encore trop près. Lila dit stop. Lila s'éloigne. Maman, le parent au parc, est au banc. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8756,6 +8892,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -8923,6 +9060,11 @@
           <t>narrateur|Tom s'approche trop près. On entend un oiseau. Lila dit stop. Lila s'éloigne. Le seau bleu reste près du banc. Lila rejoint maman, le parent au parc. Merci maman.</t>
         </is>
       </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -9090,6 +9232,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -9257,6 +9400,11 @@
           <t>narrateur|Léa s'approche trop près. Ça sent l'herbe coupée. Lila dit stop. Lila s'éloigne. Le seau bleu reste près du banc. Lila rejoint maman, le parent au parc. Merci maman.</t>
         </is>
       </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9424,6 +9572,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9591,6 +9740,11 @@
           <t>narrateur|Sami s'approche trop près. Le soleil chauffe un peu. Lila dit stop. Lila s'éloigne. Le seau bleu reste près du banc. Lila rejoint maman, le parent au parc. Merci maman.</t>
         </is>
       </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9758,6 +9912,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9925,6 +10080,11 @@
           <t>narrateur|Lila pose le doudou. Le soleil chauffe un peu. Encore trop près. Lila dit stop. Lila s'éloigne. Maman, le parent au parc, est au banc. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -10120,6 +10280,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -10287,6 +10448,11 @@
           <t>narrateur|Tom s'approche trop près. Ça sent l'herbe coupée. Lila dit stop. Lila s'éloigne. Le doudou reste près du banc. Lila rejoint maman, le parent au parc. Merci maman.</t>
         </is>
       </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10454,6 +10620,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10621,6 +10788,11 @@
           <t>narrateur|Léa s'approche trop près. Le soleil chauffe un peu. Lila dit stop. Lila s'éloigne. Le doudou reste près du banc. Lila rejoint maman, le parent au parc. Merci maman.</t>
         </is>
       </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10788,6 +10960,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10955,6 +11128,11 @@
           <t>narrateur|Sami s'approche trop près. Le sol est frais. Lila dit stop. Lila s'éloigne. Le doudou reste près du banc. Lila rejoint maman, le parent au parc. Merci maman.</t>
         </is>
       </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -11122,6 +11300,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -11289,6 +11468,11 @@
           <t>narrateur|C'est le soir. On entend un oiseau. Au parc, un camarade bouscule. Lila dit stop. Lila s'éloigne. Elle va vers maman, le parent au parc.</t>
         </is>
       </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11472,6 +11656,7 @@
           <t>narrateur|Un camarade bouscule Lila. Que fait-elle ?</t>
         </is>
       </c>
+      <c r="AX61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -11643,6 +11828,11 @@
           <t>narrateur|Oui. Stop. Lila s'éloigne. Maman est le parent au parc. On continue.</t>
         </is>
       </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11834,6 +12024,7 @@
           <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
         </is>
       </c>
+      <c r="AX63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -12001,6 +12192,11 @@
           <t>narrateur|Lila pose le ballon rouge. On entend un oiseau. Encore trop près. Lila dit stop. Lila s'éloigne. Maman, le parent au parc, est au banc. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -12196,6 +12392,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -12363,6 +12560,11 @@
           <t>narrateur|Tom s'approche trop près. On entend un oiseau. Lila dit stop. Lila s'éloigne. Le ballon rouge reste près du banc. Lila rejoint maman, le parent au parc. Merci maman.</t>
         </is>
       </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12530,6 +12732,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12697,6 +12900,11 @@
           <t>narrateur|Léa s'approche trop près. Ça sent l'herbe coupée. Lila dit stop. Lila s'éloigne. Le ballon rouge reste près du banc. Lila rejoint maman, le parent au parc. Merci maman.</t>
         </is>
       </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12864,6 +13072,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -13031,6 +13240,11 @@
           <t>narrateur|Sami s'approche trop près. Le soleil chauffe un peu. Lila dit stop. Lila s'éloigne. Le ballon rouge reste près du banc. Lila rejoint maman, le parent au parc. Merci maman.</t>
         </is>
       </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -13198,6 +13412,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -13365,6 +13580,11 @@
           <t>narrateur|Lila pose le seau bleu. Ça sent l'herbe coupée. Encore trop près. Lila dit stop. Lila s'éloigne. Maman, le parent au parc, est au banc. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13560,6 +13780,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -13727,6 +13948,11 @@
           <t>narrateur|Tom s'approche trop près. Ça sent l'herbe coupée. Lila dit stop. Lila s'éloigne. Le seau bleu reste près du banc. Lila rejoint maman, le parent au parc. Merci maman.</t>
         </is>
       </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13894,6 +14120,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -14061,6 +14288,11 @@
           <t>narrateur|Léa s'approche trop près. Le soleil chauffe un peu. Lila dit stop. Lila s'éloigne. Le seau bleu reste près du banc. Lila rejoint maman, le parent au parc. Merci maman.</t>
         </is>
       </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -14228,6 +14460,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -14395,6 +14628,11 @@
           <t>narrateur|Sami s'approche trop près. Le sol est frais. Lila dit stop. Lila s'éloigne. Le seau bleu reste près du banc. Lila rejoint maman, le parent au parc. Merci maman.</t>
         </is>
       </c>
+      <c r="AX78" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14562,6 +14800,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14729,6 +14968,11 @@
           <t>narrateur|Lila pose le doudou. Le soleil chauffe un peu. Encore trop près. Lila dit stop. Lila s'éloigne. Maman, le parent au parc, est au banc. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX80" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14924,6 +15168,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -15091,6 +15336,11 @@
           <t>narrateur|Tom s'approche trop près. Le soleil chauffe un peu. Lila dit stop. Lila s'éloigne. Le doudou reste près du banc. Lila rejoint maman, le parent au parc. Merci maman.</t>
         </is>
       </c>
+      <c r="AX82" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -15258,6 +15508,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -15425,6 +15676,11 @@
           <t>narrateur|Léa s'approche trop près. Le sol est frais. Lila dit stop. Lila s'éloigne. Le doudou reste près du banc. Lila rejoint maman, le parent au parc. Merci maman.</t>
         </is>
       </c>
+      <c r="AX84" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15592,6 +15848,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15759,6 +16016,11 @@
           <t>narrateur|Sami s'approche trop près. Un petit bruit d'eau. Lila dit stop. Lila s'éloigne. Le doudou reste près du banc. Lila rejoint maman, le parent au parc. Merci maman.</t>
         </is>
       </c>
+      <c r="AX86" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15926,6 +16188,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX87" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15944,7 +16207,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A11"/>
+  <dimension ref="A1:A13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -16024,6 +16287,20 @@
       <c r="A11" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -16038,7 +16315,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -16225,6 +16502,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
